--- a/docs/accessibility/accessibility-test-cases-spanish.xlsx
+++ b/docs/accessibility/accessibility-test-cases-spanish.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automated Accessibility" sheetId="1" r:id="R96edb739995445c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Accessibility" sheetId="2" r:id="R82b99b5af73c4e61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="3" r:id="R9894edd882ca4609"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCAG Coverage Matrix" sheetId="4" r:id="R30c179caf49c4f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automated Accessibility" sheetId="1" r:id="R5fc33b742c4747f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Accessibility" sheetId="2" r:id="R14faf9a0a3da4268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="3" r:id="R32854f9851304b6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCAG Coverage Matrix" sheetId="4" r:id="R217a1174b62a4107"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,7 +467,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>6 casos TestNG planificados; 13 escaneos obligatorios. Sin resultados de ejecución.</x:v>
+        <x:v>6 casos implementados; 13 scans completados el 2026-10-09. PASS; revisión de incomplete pendiente.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
@@ -566,10 +566,10 @@
         <x:v>Allure futuro: ID caso/estado, URL, fecha-hora, entorno, versión/configuración axe, resultados estructurados, regla/impacto/etiquetas, nodos, incomplete y errores técnicos. Aún no existe evidencia.</x:v>
       </x:c>
       <x:c r="N6" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O6" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P6" s="6" t="str">
         <x:v>Not Evaluated</x:v>
@@ -621,10 +621,10 @@
         <x:v>Allure futuro: ID caso/estado, URL, fecha-hora, entorno, versión/configuración axe, resultados estructurados, regla/impacto/etiquetas, nodos, incomplete y errores técnicos. Aún no existe evidencia.</x:v>
       </x:c>
       <x:c r="N7" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O7" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P7" s="11" t="str">
         <x:v>Not Evaluated</x:v>
@@ -675,10 +675,10 @@
         <x:v>Allure futuro: ID caso/estado, URL, fecha-hora, entorno, versión/configuración axe, resultados estructurados, regla/impacto/etiquetas, nodos, incomplete y errores técnicos. Aún no existe evidencia.</x:v>
       </x:c>
       <x:c r="N8" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O8" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P8" s="6" t="str">
         <x:v>Not Evaluated</x:v>
@@ -732,10 +732,10 @@
         <x:v>Allure futuro: ID caso/estado, URL, fecha-hora, entorno, versión/configuración axe, resultados estructurados, regla/impacto/etiquetas, nodos, incomplete y errores técnicos. Aún no existe evidencia.</x:v>
       </x:c>
       <x:c r="N9" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O9" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P9" s="11" t="str">
         <x:v>Not Evaluated</x:v>
@@ -785,10 +785,10 @@
         <x:v>Allure futuro: ID caso/estado, URL, fecha-hora, entorno, versión/configuración axe, resultados estructurados, regla/impacto/etiquetas, nodos, incomplete y errores técnicos. Aún no existe evidencia.</x:v>
       </x:c>
       <x:c r="N10" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O10" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P10" s="6" t="str">
         <x:v>Not Evaluated</x:v>
@@ -838,10 +838,10 @@
         <x:v>Allure futuro: ID caso/estado, URL, fecha-hora, entorno, versión/configuración axe, resultados estructurados, regla/impacto/etiquetas, nodos, incomplete y errores técnicos. Aún no existe evidencia.</x:v>
       </x:c>
       <x:c r="N11" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O11" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P11" s="11" t="str">
         <x:v>Not Evaluated</x:v>
@@ -850,7 +850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64d61517324543b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R120c11053f544c52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1381,7 +1381,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7cc0ed3e00045cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8cd776b2a474307"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1662,7 +1662,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38dad38a18884236"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb40b29e797544aa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1789,16 +1789,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L6" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M6" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N6" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag111 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O6" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/non-text-content.html</x:v>
@@ -1839,7 +1839,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K7" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -1848,7 +1848,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N7" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag121. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O7" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-only-and-video-only-prerecorded.html</x:v>
@@ -1889,16 +1889,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K8" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L8" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M8" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N8" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag122 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O8" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/captions-prerecorded.html</x:v>
@@ -1939,7 +1939,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K9" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -1948,7 +1948,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N9" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag123. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O9" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-description-or-media-alternative-prerecorded.html</x:v>
@@ -1989,7 +1989,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K10" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L10" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -1998,7 +1998,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N10" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag124. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O10" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/captions-live.html</x:v>
@@ -2039,7 +2039,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K11" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2048,7 +2048,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N11" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag125. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O11" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-description-prerecorded.html</x:v>
@@ -2089,16 +2089,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K12" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L12" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M12" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N12" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag131 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O12" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/info-and-relationships.html</x:v>
@@ -2139,7 +2139,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K13" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2148,7 +2148,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N13" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag132. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O13" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/meaningful-sequence.html</x:v>
@@ -2189,7 +2189,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L14" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -2198,7 +2198,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N14" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag133. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O14" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/sensory-characteristics.html</x:v>
@@ -2239,16 +2239,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K15" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M15" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N15" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag134 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O15" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/orientation.html</x:v>
@@ -2289,16 +2289,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K16" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L16" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M16" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N16" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag135 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O16" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/identify-input-purpose.html</x:v>
@@ -2339,16 +2339,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K17" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M17" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N17" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag141 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O17" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/use-of-color.html</x:v>
@@ -2389,16 +2389,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K18" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L18" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M18" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N18" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag142 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O18" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-control.html</x:v>
@@ -2439,16 +2439,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K19" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M19" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N19" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag143 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O19" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/contrast-minimum.html</x:v>
@@ -2489,16 +2489,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L20" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M20" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N20" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag144 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O20" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/resize-text.html</x:v>
@@ -2539,7 +2539,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K21" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2548,7 +2548,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N21" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag145. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O21" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/images-of-text.html</x:v>
@@ -2589,7 +2589,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K22" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L22" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -2598,7 +2598,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N22" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag1410. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O22" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/reflow.html</x:v>
@@ -2639,7 +2639,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K23" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2648,7 +2648,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N23" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag1411. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O23" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/non-text-contrast.html</x:v>
@@ -2689,16 +2689,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K24" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L24" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M24" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N24" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag1412 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O24" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/text-spacing.html</x:v>
@@ -2739,7 +2739,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K25" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2748,7 +2748,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N25" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag1413. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O25" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/content-on-hover-or-focus.html</x:v>
@@ -2789,16 +2789,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K26" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L26" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M26" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N26" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag211 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O26" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/keyboard.html</x:v>
@@ -2839,7 +2839,7 @@
         <x:v>Se incluye el menú lateral abierto. La expansión del submenú no es un escaneo automatizado obligatorio separado; no se debe entrar a rutas excluidas.</x:v>
       </x:c>
       <x:c r="K27" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2848,7 +2848,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N27" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag212. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O27" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/no-keyboard-trap.html</x:v>
@@ -2889,7 +2889,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K28" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L28" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -2898,7 +2898,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N28" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag214. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O28" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/character-key-shortcuts.html</x:v>
@@ -2939,16 +2939,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K29" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M29" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N29" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag221 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O29" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/timing-adjustable.html</x:v>
@@ -2989,16 +2989,16 @@
         <x:v>Se conserva Applicable de la fuente para la aplicación ampliada. La evidencia del Slider está fuera del alcance inicial. La presencia de contenido que active el requisito en el flujo aprobado está To Be Confirmed. La ejecución manual de la ruta excluida queda diferida.</x:v>
       </x:c>
       <x:c r="K30" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L30" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M30" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N30" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag222 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O30" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/pause-stop-hide.html</x:v>
@@ -3039,7 +3039,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K31" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3048,7 +3048,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N31" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag231. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O31" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/three-flashes-or-below-threshold.html</x:v>
@@ -3089,16 +3089,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K32" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L32" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M32" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N32" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag241 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O32" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/bypass-blocks.html</x:v>
@@ -3139,16 +3139,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K33" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M33" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N33" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag242 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O33" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/page-titled.html</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K34" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L34" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3198,7 +3198,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N34" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag243. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O34" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/focus-order.html</x:v>
@@ -3239,16 +3239,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K35" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L35" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M35" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N35" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag244 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O35" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/link-purpose-in-context.html</x:v>
@@ -3289,7 +3289,7 @@
         <x:v>Evaluar navegación entre páginas aprobadas y documentar excepciones del proceso. Detalle y catálogos largo/dinámicos permanecen fuera de alcance. Sin dictamen de toda la aplicación.</x:v>
       </x:c>
       <x:c r="K36" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L36" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3298,7 +3298,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N36" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag245. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O36" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/multiple-ways.html</x:v>
@@ -3339,7 +3339,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K37" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3348,7 +3348,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N37" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag246. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O37" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/headings-and-labels.html</x:v>
@@ -3389,7 +3389,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K38" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L38" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3398,7 +3398,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N38" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag247. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O38" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/focus-visible.html</x:v>
@@ -3439,7 +3439,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K39" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3448,7 +3448,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N39" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag2411. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O39" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/focus-not-obscured-minimum.html</x:v>
@@ -3489,7 +3489,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K40" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L40" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3498,7 +3498,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N40" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag251. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O40" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/pointer-gestures.html</x:v>
@@ -3539,7 +3539,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K41" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L41" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3548,7 +3548,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N41" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag252. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O41" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/pointer-cancellation.html</x:v>
@@ -3589,16 +3589,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K42" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L42" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M42" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N42" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag253 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O42" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/label-in-name.html</x:v>
@@ -3639,7 +3639,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K43" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L43" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3648,7 +3648,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N43" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag254. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O43" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/motion-actuation.html</x:v>
@@ -3689,7 +3689,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K44" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L44" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3698,7 +3698,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N44" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag257. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O44" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/dragging-movements.html</x:v>
@@ -3739,16 +3739,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K45" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L45" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M45" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N45" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag258 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O45" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/target-size-minimum.html</x:v>
@@ -3789,16 +3789,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K46" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L46" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M46" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N46" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag311 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O46" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/language-of-page.html</x:v>
@@ -3839,16 +3839,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K47" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L47" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M47" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N47" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag312 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O47" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/language-of-parts.html</x:v>
@@ -3889,7 +3889,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K48" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L48" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3898,7 +3898,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N48" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag321. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O48" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/on-focus.html</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K49" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L49" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N49" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag322. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O49" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/on-input.html</x:v>
@@ -3989,7 +3989,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K50" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L50" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3998,7 +3998,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N50" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag323. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O50" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/consistent-navigation.html</x:v>
@@ -4039,7 +4039,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K51" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L51" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4048,7 +4048,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N51" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag324. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O51" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/consistent-identification.html</x:v>
@@ -4089,7 +4089,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K52" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L52" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4098,7 +4098,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N52" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag326. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O52" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/consistent-help.html</x:v>
@@ -4139,7 +4139,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K53" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L53" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4148,7 +4148,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N53" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag331. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O53" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/error-identification.html</x:v>
@@ -4189,16 +4189,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K54" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L54" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M54" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N54" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag332 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O54" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/labels-or-instructions.html</x:v>
@@ -4239,7 +4239,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K55" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L55" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4248,7 +4248,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N55" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag333. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O55" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/error-suggestion.html</x:v>
@@ -4289,7 +4289,7 @@
         <x:v>Evaluar revisión y efectos del pedido dentro del proceso aprobado. Reset App State permanece como pregunta de aplicabilidad, sin añadir un escaneo automatizado.</x:v>
       </x:c>
       <x:c r="K56" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L56" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4298,7 +4298,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N56" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag334. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O56" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/error-prevention-legal-financial-data.html</x:v>
@@ -4339,7 +4339,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K57" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L57" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4348,7 +4348,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N57" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag337. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O57" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/redundant-entry.html</x:v>
@@ -4389,7 +4389,7 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K58" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L58" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4398,7 +4398,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N58" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag338. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O58" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/accessible-authentication-minimum.html</x:v>
@@ -4439,16 +4439,16 @@
         <x:v>Evaluar solo los estados aprobados. Las funciones adicionales y la ausencia de contenido que active un requisito requieren confirmación. Las relaciones con casos describen cobertura parcial planificada, no verificación realizada.</x:v>
       </x:c>
       <x:c r="K59" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L59" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M59" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N59" s="11" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: reglas con wcag412 ejecutadas en estados vinculados. Ver Test Results y execution-summary.json. Cobertura parcial; revisión manual pendiente. Criterio Not Evaluated. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O59" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/name-role-value.html</x:v>
@@ -4489,7 +4489,7 @@
         <x:v>Solo se planifican errores y cambios del carrito en estados aprobados. Spinner y otras rutas dinámicas permanecen excluidos.</x:v>
       </x:c>
       <x:c r="K60" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L60" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4498,7 +4498,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N60" s="6" t="str">
-        <x:v>REF-02 §2 (incorporado en Test Data, REF-02): esta fila y su aclaración de alcance reproducen observaciones estáticas históricas, no resultados de estados renderizados. Sin evidencia de ejecución axe/NVDA/manual. Confirmar aplicabilidad y evaluar dentro de alcance; no se registraron fecha ni referencia de versión inspeccionada.</x:v>
+        <x:v>axe 4.13.0: sin regla seleccionada con wcag413. Los vínculos provisionales no prueban ejecución del criterio. Evaluación manual Planned / Not Executed. REF-02 conserva observaciones históricas.</x:v>
       </x:c>
       <x:c r="O60" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/status-messages.html</x:v>
@@ -4518,7 +4518,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ff67f8c073493c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e4ce0121dc9446c"/>
   </x:tableParts>
 </x:worksheet>
 </file>